--- a/AAII_Financials/Quarterly/DUO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DUO_QTR_FIN.xlsx
@@ -1380,10 +1380,10 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>700</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1813,10 +1813,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-1300</v>
+        <v>-700</v>
       </c>
       <c r="E21" s="3">
-        <v>-1300</v>
+        <v>-700</v>
       </c>
       <c r="F21" s="3">
         <v>-3100</v>
@@ -3548,10 +3548,10 @@
         <v>30500</v>
       </c>
       <c r="F43" s="3">
-        <v>32400</v>
+        <v>33500</v>
       </c>
       <c r="G43" s="3">
-        <v>32000</v>
+        <v>33100</v>
       </c>
       <c r="H43" s="3">
         <v>43000</v>
@@ -3732,10 +3732,10 @@
         <v>2800</v>
       </c>
       <c r="F45" s="3">
-        <v>4800</v>
+        <v>3700</v>
       </c>
       <c r="G45" s="3">
-        <v>4800</v>
+        <v>3600</v>
       </c>
       <c r="H45" s="3">
         <v>3600</v>
